--- a/public/template-import-produse.xlsx
+++ b/public/template-import-produse.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -506,8 +506,9 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,6 +554,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>pret_culori</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>specificatii</t>
         </is>
       </c>
@@ -600,6 +606,11 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Preț pe culoare: „Culoare: preț;” (opțional)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>Cheie: valoare; separate prin ;</t>
         </is>
       </c>
@@ -647,10 +658,15 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>Cărămiziu: 42.90; Antracit: 45.90; Negru mat: 47.00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>Grosime: 0.5 mm; Garanție: 15 ani; Greutate: 4.8 kg/mp</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>◄ EXEMPLE — șterge aceste 2 rânduri și completează de la rândul 3 în jos</t>
         </is>
@@ -693,7 +709,8 @@
           <t>Maro, Antracit</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Diametru: Ø150 mm; Material: Oțel 0.6mm; Lungime: 3 m/buc</t>
         </is>
@@ -709,6 +726,7 @@
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -720,6 +738,7 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -731,6 +750,7 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -742,6 +762,7 @@
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -753,6 +774,7 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -764,6 +786,7 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -775,6 +798,7 @@
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -786,6 +810,7 @@
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -797,6 +822,7 @@
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -808,6 +834,7 @@
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -819,6 +846,7 @@
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -830,6 +858,7 @@
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -841,6 +870,7 @@
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -852,6 +882,7 @@
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -863,6 +894,7 @@
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -874,6 +906,7 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -885,6 +918,7 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -896,6 +930,7 @@
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -907,6 +942,7 @@
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -918,6 +954,7 @@
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -929,6 +966,7 @@
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -940,6 +978,7 @@
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -951,6 +990,7 @@
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -962,6 +1002,7 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -973,6 +1014,7 @@
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -984,6 +1026,7 @@
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -995,6 +1038,7 @@
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1006,6 +1050,7 @@
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1017,6 +1062,7 @@
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1028,6 +1074,7 @@
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1039,6 +1086,7 @@
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1050,6 +1098,7 @@
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1061,6 +1110,7 @@
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1072,6 +1122,7 @@
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1083,6 +1134,7 @@
       <c r="G39" s="5" t="n"/>
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1094,6 +1146,7 @@
       <c r="G40" s="5" t="n"/>
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1105,6 +1158,7 @@
       <c r="G41" s="5" t="n"/>
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1116,6 +1170,7 @@
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1127,6 +1182,7 @@
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1138,6 +1194,7 @@
       <c r="G44" s="5" t="n"/>
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -1149,6 +1206,7 @@
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -1160,6 +1218,7 @@
       <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -1171,6 +1230,7 @@
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -1182,6 +1242,7 @@
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -1193,6 +1254,7 @@
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -1204,6 +1266,7 @@
       <c r="G50" s="5" t="n"/>
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -1215,6 +1278,7 @@
       <c r="G51" s="5" t="n"/>
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -1226,6 +1290,7 @@
       <c r="G52" s="5" t="n"/>
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -1237,6 +1302,7 @@
       <c r="G53" s="5" t="n"/>
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -1248,6 +1314,7 @@
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -1259,6 +1326,7 @@
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -1270,6 +1338,7 @@
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -1281,6 +1350,7 @@
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -1292,6 +1362,7 @@
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -1303,6 +1374,7 @@
       <c r="G59" s="5" t="n"/>
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1326,7 +1398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1483,26 +1555,38 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>pret_culori</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Preț DIFERIT pe culoare (opțional): „Culoare: preț;”. Ex: Antracit: 45.90; Cărămiziu: 42.90. Dacă e gol, se folosește prețul de bază.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>specificatii</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Perechi „Cheie: valoare” separate prin punct și virgulă (;). Ex: Grosime: 0.5 mm; Garanție: 15 ani</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr"/>
-      <c r="B16" s="8" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Notă</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Prețurile pe finisaj/grosime și culorile per finisaj le poți ajusta ulterior din admin, la fiecare produs.</t>
         </is>

--- a/public/template-import-produse.xlsx
+++ b/public/template-import-produse.xlsx
@@ -513,20 +513,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -569,25 +570,30 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>producator</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>finisaj</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>culoare</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>grosime</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>pret</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>specificatii</t>
         </is>
@@ -626,25 +632,30 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Ruukki</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Poliester mat</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Cărămiziu</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>0.50 mm</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>42.90</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Acoperire: Poliester mat 25µm; Garanție: 15 ani</t>
         </is>
@@ -661,27 +672,28 @@
       <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Poliester mat</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Cărămiziu</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>0.60 mm</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>51.90</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -694,27 +706,28 @@
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Poliester mat</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Antracit</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>0.50 mm</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>44.90</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -727,27 +740,28 @@
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Poliester mat</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Antracit</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>0.60 mm</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>53.90</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -760,27 +774,28 @@
       <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Mat structurat</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Cărămiziu</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>0.50 mm</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>49.90</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -793,27 +808,28 @@
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr"/>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Mat structurat</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Cărămiziu</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>0.60 mm</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>58.90</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -826,27 +842,28 @@
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
       <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Mat structurat</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Antracit</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>0.50 mm</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>51.90</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -859,27 +876,28 @@
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="6" t="inlineStr"/>
       <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Mat structurat</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Antracit</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>0.60 mm</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>60.90</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -910,21 +928,26 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>Lindab</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>Lucios</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Antracit</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>23.50</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Diametru: 125 mm; Lungime: 3 m</t>
         </is>
@@ -941,27 +964,28 @@
       <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Lucios</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Alb</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>22.00</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -973,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1089,64 +1113,71 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>finisaj        – numele finisajului (ex: Poliester mat). Vezi „Valori permise”.</t>
+          <t>producator     – numele producătorului / brandului (ex: Ruukki, Lindab). Opțional. Doar pe primul rând.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>culoare        – numele culorii (ex: Antracit). Lasă gol dacă produsul nu are culori.</t>
+          <t>finisaj        – numele finisajului (ex: Poliester mat). Vezi „Valori permise”.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>grosime        – ex: 0.50 mm. Lasă gol dacă produsul nu are grosimi.</t>
+          <t>culoare        – numele culorii (ex: Antracit). Lasă gol dacă produsul nu are culori.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>pret           – prețul final (lei) al combinației de pe rândul respectiv. Ex: 42.90</t>
+          <t>grosime        – ex: 0.50 mm. Lasă gol dacă produsul nu are grosimi.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
+          <t>pret           – prețul final (lei) al combinației de pe rândul respectiv. Ex: 42.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
           <t>specificatii   – „Cheie: valoare; Cheie: valoare”. Doar pe primul rând.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Sfaturi:</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>• Numele de finisaj/culoare/grosime care nu există încă în tab-ul „Proprietăți” se importă oricum, dar adaugă-le acolo ca să apară numele frumos și pastila de culoare corectă.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>• Poți salva ca .csv (delimitat prin virgulă) și importa la fel.</t>
+          <t>• Numele de finisaj/culoare/grosime care nu există încă în tab-ul „Proprietăți” se importă oricum, dar adaugă-le acolo ca să apară numele frumos și pastila de culoare corectă.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>• Poți salva ca .csv (delimitat prin virgulă) și importa la fel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>• Un produs simplu (fără finisaje) poate fi importat cu formatul vechi: coloane „pret”, „culori”, „pret_culori” în loc de finisaj/culoare/grosime — dar recomandat e formatul de mai sus.</t>
         </is>
